--- a/MultiCellBMSConfig/NMC/Experiment_5_NMC_Configuration.xlsx
+++ b/MultiCellBMSConfig/NMC/Experiment_5_NMC_Configuration.xlsx
@@ -461,6 +461,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -572,7 +573,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">   - Variable-Length CAN Mode: Set parser_type = 'waveshare_can' or 'variable_length' (Header 0xAA, DLC, CAN ID, payload, footer 0x55).</t>
+          <t xml:space="preserve">   - Variable-Length CAN Mode: Set parser_type = 'waveshare_can_variable_length' (Variable-Length CAN) (Header 0xAA, DLC, CAN ID, payload, footer 0x55).</t>
         </is>
       </c>
     </row>
@@ -590,6 +591,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -938,7 +940,6 @@
           <t>header_to_payload</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>none</t>
@@ -962,7 +963,7 @@
   </sheetData>
   <dataValidations count="13">
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"framed,waveshare_can,waveshare_can_20_bytes"</formula1>
+      <formula1>"framed,waveshare_can_variable_length,waveshare_can_20_bytes"</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"1,2,4"</formula1>
@@ -1525,7 +1526,6 @@
       <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>little</t>
@@ -1586,7 +1586,6 @@
       <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>little</t>
@@ -1899,7 +1898,6 @@
       <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
           <t>little</t>
@@ -2149,7 +2147,6 @@
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
           <t>little</t>
@@ -2273,7 +2270,6 @@
       <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
           <t>little</t>
@@ -2334,7 +2330,6 @@
       <c r="D15" t="n">
         <v>1</v>
       </c>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
           <t>little</t>
@@ -2395,7 +2390,6 @@
       <c r="D16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>little</t>
@@ -2456,7 +2450,6 @@
       <c r="D17" t="n">
         <v>1</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
           <t>little</t>
@@ -2517,7 +2510,6 @@
       <c r="D18" t="n">
         <v>1</v>
       </c>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
           <t>little</t>
@@ -2578,7 +2570,6 @@
       <c r="D19" t="n">
         <v>1</v>
       </c>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
           <t>little</t>
@@ -2639,7 +2630,6 @@
       <c r="D20" t="n">
         <v>1</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
           <t>little</t>
@@ -2700,7 +2690,6 @@
       <c r="D21" t="n">
         <v>1</v>
       </c>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
           <t>little</t>
@@ -3726,7 +3715,6 @@
           <t>V</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="b">
         <v>1</v>
       </c>
@@ -3747,7 +3735,6 @@
           <t>V</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="b">
         <v>1</v>
       </c>
@@ -3768,7 +3755,6 @@
           <t>°C</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="b">
         <v>1</v>
       </c>
